--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/INDIANA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/INDIANA_2011.xlsx
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C163">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C629">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C968">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C989">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1107">
